--- a/stress_data_avg.xlsx
+++ b/stress_data_avg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Documents\githubb\Educational Psychology\EPSY-5123-Final-Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torra034\Documents\githubb\Educational Psychology\EPSY-5123-Final-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CEF59A3-48B6-4CC0-B125-1B996BC198FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA1998-2823-4EE9-830F-20411AC1676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1425" windowWidth="14565" windowHeight="12510" xr2:uid="{BAD9A85B-C939-428E-9DAB-ED27ACC724B2}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{BAD9A85B-C939-428E-9DAB-ED27ACC724B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Date</t>
   </si>
@@ -234,6 +234,12 @@
   </si>
   <si>
     <t>Apr 6-12, 2025</t>
+  </si>
+  <si>
+    <t>Apr 6-12, 2026</t>
+  </si>
+  <si>
+    <t>Apr 13-19, 2026</t>
   </si>
 </sst>
 </file>
@@ -605,13 +611,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27989BB8-F1D0-4FB1-A6B3-819F146215A8}">
-  <dimension ref="A1:B65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -619,479 +625,495 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B8">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B11">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B12">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B13">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B14">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B16">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
+      <c r="B18">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="B19">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
+      <c r="B22">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
+      <c r="B23">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
+      <c r="B24">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
+      <c r="B26">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
+      <c r="B27">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
+      <c r="B28">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
+      <c r="B30">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
+      <c r="B32">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
+      <c r="B33">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="B32">
+      <c r="B34">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>33</v>
       </c>
-      <c r="B33">
+      <c r="B35">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
+      <c r="B37">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="B36">
+      <c r="B38">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>37</v>
       </c>
-      <c r="B37">
+      <c r="B39">
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>38</v>
       </c>
-      <c r="B38">
+      <c r="B40">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>41</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>42</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="B43">
+      <c r="B45">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
+      <c r="B46">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>46</v>
       </c>
-      <c r="B46">
+      <c r="B48">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>47</v>
       </c>
-      <c r="B47">
+      <c r="B49">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>48</v>
       </c>
-      <c r="B48">
+      <c r="B50">
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>49</v>
       </c>
-      <c r="B49">
+      <c r="B51">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>51</v>
       </c>
-      <c r="B51">
+      <c r="B53">
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>52</v>
       </c>
-      <c r="B52">
+      <c r="B54">
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>53</v>
       </c>
-      <c r="B53">
+      <c r="B55">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B54">
+      <c r="B56">
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>55</v>
       </c>
-      <c r="B55">
+      <c r="B57">
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B57">
+      <c r="B59">
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>58</v>
       </c>
-      <c r="B58">
+      <c r="B60">
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>59</v>
       </c>
-      <c r="B59">
+      <c r="B61">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>60</v>
       </c>
-      <c r="B60">
+      <c r="B62">
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>62</v>
       </c>
-      <c r="B62">
+      <c r="B64">
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>63</v>
       </c>
-      <c r="B63">
+      <c r="B65">
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>64</v>
       </c>
-      <c r="B64">
+      <c r="B66">
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>65</v>
       </c>
-      <c r="B65">
+      <c r="B67">
         <v>35</v>
       </c>
     </row>

--- a/stress_data_avg.xlsx
+++ b/stress_data_avg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torra034\Documents\githubb\Educational Psychology\EPSY-5123-Final-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA1998-2823-4EE9-830F-20411AC1676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10281B6A-806A-4428-9658-41E46339FAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{BAD9A85B-C939-428E-9DAB-ED27ACC724B2}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="14025" windowHeight="11235" xr2:uid="{BAD9A85B-C939-428E-9DAB-ED27ACC724B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>Apr 13-19, 2026</t>
+  </si>
+  <si>
+    <t>Apr 21-27, 2026</t>
   </si>
 </sst>
 </file>
@@ -611,13 +614,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27989BB8-F1D0-4FB1-A6B3-819F146215A8}">
-  <dimension ref="A1:B67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -625,495 +628,503 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>67</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>66</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>31</v>
-      </c>
-      <c r="B33">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>32</v>
       </c>
       <c r="B34">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>42</v>
-      </c>
-      <c r="B44">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>43</v>
       </c>
       <c r="B45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46">
         <v>44</v>
       </c>
-      <c r="B46">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>52</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>55</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B66">
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B67">
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>35</v>
       </c>
     </row>
